--- a/Entrega-2/v4/demo/generated/leadership_review.xlsx
+++ b/Entrega-2/v4/demo/generated/leadership_review.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookProtection workbookPassword="FE27" lockStructure="1"/>
   <sheets>
-    <sheet name="Summary" sheetId="1" ns1:id="Ra32b84bc81db473e"/>
-    <sheet name="Detail" sheetId="2" ns1:id="R951cb57d4b7a42a5"/>
+    <sheet name="Summary" sheetId="1" ns1:id="R36c27a5415224771"/>
+    <sheet name="Detail" sheetId="2" ns1:id="Rbb7011691ee74a71"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
